--- a/artfynd/A 6620-2025 artfynd.xlsx
+++ b/artfynd/A 6620-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AY20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2189,6 +2189,521 @@
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>123231136</v>
+      </c>
+      <c r="B16" t="n">
+        <v>57494</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Långstranden, Långstranden, Ång</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>585384</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7041145</v>
+      </c>
+      <c r="S16" t="n">
+        <v>15</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Ådals-Liden</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>123236444</v>
+      </c>
+      <c r="B17" t="n">
+        <v>90952</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Långstranden, Långstranden, Ång</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>585270</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7041198</v>
+      </c>
+      <c r="S17" t="n">
+        <v>15</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Ådals-Liden</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>123236145</v>
+      </c>
+      <c r="B18" t="n">
+        <v>90917</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Långstranden, Långstranden, Ång</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>585269</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7041239</v>
+      </c>
+      <c r="S18" t="n">
+        <v>15</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Ådals-Liden</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>123236869</v>
+      </c>
+      <c r="B19" t="n">
+        <v>78766</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Långstranden, Långstranden, Ång</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>585327</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7041140</v>
+      </c>
+      <c r="S19" t="n">
+        <v>15</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Ådals-Liden</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>123236897</v>
+      </c>
+      <c r="B20" t="n">
+        <v>90948</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Långstranden, Långstranden, Ång</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>585327</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7041140</v>
+      </c>
+      <c r="S20" t="n">
+        <v>15</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Ådals-Liden</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 6620-2025 artfynd.xlsx
+++ b/artfynd/A 6620-2025 artfynd.xlsx
@@ -2191,10 +2191,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123231136</v>
+        <v>123236444</v>
       </c>
       <c r="B16" t="n">
-        <v>57494</v>
+        <v>90952</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2207,39 +2207,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Långstranden, Långstranden, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>585384</v>
+        <v>585270</v>
       </c>
       <c r="R16" t="n">
-        <v>7041145</v>
+        <v>7041198</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2298,10 +2293,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123236444</v>
+        <v>123231136</v>
       </c>
       <c r="B17" t="n">
-        <v>90952</v>
+        <v>57494</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2314,34 +2309,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Långstranden, Långstranden, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>585270</v>
+        <v>585384</v>
       </c>
       <c r="R17" t="n">
-        <v>7041198</v>
+        <v>7041145</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>

--- a/artfynd/A 6620-2025 artfynd.xlsx
+++ b/artfynd/A 6620-2025 artfynd.xlsx
@@ -2191,10 +2191,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123236444</v>
+        <v>123236869</v>
       </c>
       <c r="B16" t="n">
-        <v>90952</v>
+        <v>78766</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2207,21 +2207,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2231,10 +2231,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>585270</v>
+        <v>585327</v>
       </c>
       <c r="R16" t="n">
-        <v>7041198</v>
+        <v>7041140</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2293,10 +2293,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123231136</v>
+        <v>123236145</v>
       </c>
       <c r="B17" t="n">
-        <v>57494</v>
+        <v>90917</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2305,43 +2305,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Långstranden, Långstranden, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>585384</v>
+        <v>585269</v>
       </c>
       <c r="R17" t="n">
-        <v>7041145</v>
+        <v>7041239</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2400,10 +2395,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123236145</v>
+        <v>123236444</v>
       </c>
       <c r="B18" t="n">
-        <v>90917</v>
+        <v>90952</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2412,25 +2407,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2440,10 +2435,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>585269</v>
+        <v>585270</v>
       </c>
       <c r="R18" t="n">
-        <v>7041239</v>
+        <v>7041198</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2502,10 +2497,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123236869</v>
+        <v>123231136</v>
       </c>
       <c r="B19" t="n">
-        <v>78766</v>
+        <v>57494</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2518,34 +2513,39 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Långstranden, Långstranden, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>585327</v>
+        <v>585384</v>
       </c>
       <c r="R19" t="n">
-        <v>7041140</v>
+        <v>7041145</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>

--- a/artfynd/A 6620-2025 artfynd.xlsx
+++ b/artfynd/A 6620-2025 artfynd.xlsx
@@ -2191,10 +2191,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123236869</v>
+        <v>123236897</v>
       </c>
       <c r="B16" t="n">
-        <v>78766</v>
+        <v>90948</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2207,21 +2207,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2293,10 +2293,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123236145</v>
+        <v>123236869</v>
       </c>
       <c r="B17" t="n">
-        <v>90917</v>
+        <v>78766</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2305,25 +2305,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2333,10 +2333,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>585269</v>
+        <v>585327</v>
       </c>
       <c r="R17" t="n">
-        <v>7041239</v>
+        <v>7041140</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2395,10 +2395,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123236444</v>
+        <v>123231136</v>
       </c>
       <c r="B18" t="n">
-        <v>90952</v>
+        <v>57494</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2411,34 +2411,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Långstranden, Långstranden, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>585270</v>
+        <v>585384</v>
       </c>
       <c r="R18" t="n">
-        <v>7041198</v>
+        <v>7041145</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2497,10 +2502,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123231136</v>
+        <v>123236444</v>
       </c>
       <c r="B19" t="n">
-        <v>57494</v>
+        <v>90952</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2513,39 +2518,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Långstranden, Långstranden, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>585384</v>
+        <v>585270</v>
       </c>
       <c r="R19" t="n">
-        <v>7041145</v>
+        <v>7041198</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2604,10 +2604,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123236897</v>
+        <v>123236145</v>
       </c>
       <c r="B20" t="n">
-        <v>90948</v>
+        <v>90917</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2616,25 +2616,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1108</v>
+        <v>5447</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2644,10 +2644,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>585327</v>
+        <v>585269</v>
       </c>
       <c r="R20" t="n">
-        <v>7041140</v>
+        <v>7041239</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>

--- a/artfynd/A 6620-2025 artfynd.xlsx
+++ b/artfynd/A 6620-2025 artfynd.xlsx
@@ -2191,10 +2191,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123236897</v>
+        <v>123236869</v>
       </c>
       <c r="B16" t="n">
-        <v>90948</v>
+        <v>78769</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2207,21 +2207,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2293,10 +2293,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123236869</v>
+        <v>123236444</v>
       </c>
       <c r="B17" t="n">
-        <v>78766</v>
+        <v>90955</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2309,21 +2309,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2333,10 +2333,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>585327</v>
+        <v>585270</v>
       </c>
       <c r="R17" t="n">
-        <v>7041140</v>
+        <v>7041198</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2395,10 +2395,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123231136</v>
+        <v>123236897</v>
       </c>
       <c r="B18" t="n">
-        <v>57494</v>
+        <v>90951</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2411,39 +2411,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>1108</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Långstranden, Långstranden, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>585384</v>
+        <v>585327</v>
       </c>
       <c r="R18" t="n">
-        <v>7041145</v>
+        <v>7041140</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2502,10 +2497,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123236444</v>
+        <v>123236145</v>
       </c>
       <c r="B19" t="n">
-        <v>90952</v>
+        <v>90920</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2514,25 +2509,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2542,10 +2537,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>585270</v>
+        <v>585269</v>
       </c>
       <c r="R19" t="n">
-        <v>7041198</v>
+        <v>7041239</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2604,10 +2599,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123236145</v>
+        <v>123231136</v>
       </c>
       <c r="B20" t="n">
-        <v>90917</v>
+        <v>57497</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2616,38 +2611,43 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Långstranden, Långstranden, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>585269</v>
+        <v>585384</v>
       </c>
       <c r="R20" t="n">
-        <v>7041239</v>
+        <v>7041145</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>

--- a/artfynd/A 6620-2025 artfynd.xlsx
+++ b/artfynd/A 6620-2025 artfynd.xlsx
@@ -2191,10 +2191,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123236869</v>
+        <v>123236145</v>
       </c>
       <c r="B16" t="n">
-        <v>78769</v>
+        <v>90922</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2203,25 +2203,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2231,10 +2231,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>585327</v>
+        <v>585269</v>
       </c>
       <c r="R16" t="n">
-        <v>7041140</v>
+        <v>7041239</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2293,10 +2293,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123236444</v>
+        <v>123231136</v>
       </c>
       <c r="B17" t="n">
-        <v>90955</v>
+        <v>57497</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2309,34 +2309,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Långstranden, Långstranden, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>585270</v>
+        <v>585384</v>
       </c>
       <c r="R17" t="n">
-        <v>7041198</v>
+        <v>7041145</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2398,7 +2403,7 @@
         <v>123236897</v>
       </c>
       <c r="B18" t="n">
-        <v>90951</v>
+        <v>90953</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2497,10 +2502,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123236145</v>
+        <v>123236869</v>
       </c>
       <c r="B19" t="n">
-        <v>90920</v>
+        <v>78771</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2509,25 +2514,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2537,10 +2542,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>585269</v>
+        <v>585327</v>
       </c>
       <c r="R19" t="n">
-        <v>7041239</v>
+        <v>7041140</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2599,10 +2604,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123231136</v>
+        <v>123236444</v>
       </c>
       <c r="B20" t="n">
-        <v>57497</v>
+        <v>90957</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2615,39 +2620,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Långstranden, Långstranden, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>585384</v>
+        <v>585270</v>
       </c>
       <c r="R20" t="n">
-        <v>7041145</v>
+        <v>7041198</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>

--- a/artfynd/A 6620-2025 artfynd.xlsx
+++ b/artfynd/A 6620-2025 artfynd.xlsx
@@ -2191,10 +2191,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123236145</v>
+        <v>123236869</v>
       </c>
       <c r="B16" t="n">
-        <v>90922</v>
+        <v>78772</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2203,25 +2203,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2231,10 +2231,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>585269</v>
+        <v>585327</v>
       </c>
       <c r="R16" t="n">
-        <v>7041239</v>
+        <v>7041140</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2293,10 +2293,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123231136</v>
+        <v>123236444</v>
       </c>
       <c r="B17" t="n">
-        <v>57497</v>
+        <v>90963</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2309,39 +2309,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Långstranden, Långstranden, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>585384</v>
+        <v>585270</v>
       </c>
       <c r="R17" t="n">
-        <v>7041145</v>
+        <v>7041198</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2403,7 +2398,7 @@
         <v>123236897</v>
       </c>
       <c r="B18" t="n">
-        <v>90953</v>
+        <v>90959</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2502,10 +2497,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123236869</v>
+        <v>123236145</v>
       </c>
       <c r="B19" t="n">
-        <v>78771</v>
+        <v>90928</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2514,25 +2509,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2542,10 +2537,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>585327</v>
+        <v>585269</v>
       </c>
       <c r="R19" t="n">
-        <v>7041140</v>
+        <v>7041239</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2604,10 +2599,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123236444</v>
+        <v>123231136</v>
       </c>
       <c r="B20" t="n">
-        <v>90957</v>
+        <v>57497</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2620,34 +2615,39 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Långstranden, Långstranden, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>585270</v>
+        <v>585384</v>
       </c>
       <c r="R20" t="n">
-        <v>7041198</v>
+        <v>7041145</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>

--- a/artfynd/A 6620-2025 artfynd.xlsx
+++ b/artfynd/A 6620-2025 artfynd.xlsx
@@ -2194,7 +2194,7 @@
         <v>123236897</v>
       </c>
       <c r="B16" t="n">
-        <v>90962</v>
+        <v>90979</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2293,10 +2293,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123231136</v>
+        <v>123236444</v>
       </c>
       <c r="B17" t="n">
-        <v>57497</v>
+        <v>90983</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2309,39 +2309,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Långstranden, Långstranden, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>585384</v>
+        <v>585270</v>
       </c>
       <c r="R17" t="n">
-        <v>7041145</v>
+        <v>7041198</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2403,7 +2398,7 @@
         <v>123236869</v>
       </c>
       <c r="B18" t="n">
-        <v>78775</v>
+        <v>78781</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2502,10 +2497,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123236145</v>
+        <v>123231136</v>
       </c>
       <c r="B19" t="n">
-        <v>90931</v>
+        <v>57503</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2514,38 +2509,43 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Långstranden, Långstranden, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>585269</v>
+        <v>585384</v>
       </c>
       <c r="R19" t="n">
-        <v>7041239</v>
+        <v>7041145</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2604,10 +2604,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123236444</v>
+        <v>123236145</v>
       </c>
       <c r="B20" t="n">
-        <v>90966</v>
+        <v>90948</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2616,25 +2616,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2644,10 +2644,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>585270</v>
+        <v>585269</v>
       </c>
       <c r="R20" t="n">
-        <v>7041198</v>
+        <v>7041239</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>

--- a/artfynd/A 6620-2025 artfynd.xlsx
+++ b/artfynd/A 6620-2025 artfynd.xlsx
@@ -2194,7 +2194,7 @@
         <v>123236897</v>
       </c>
       <c r="B16" t="n">
-        <v>90979</v>
+        <v>90984</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2296,7 +2296,7 @@
         <v>123236444</v>
       </c>
       <c r="B17" t="n">
-        <v>90983</v>
+        <v>90988</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2398,7 +2398,7 @@
         <v>123236869</v>
       </c>
       <c r="B18" t="n">
-        <v>78781</v>
+        <v>78786</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2500,7 +2500,7 @@
         <v>123231136</v>
       </c>
       <c r="B19" t="n">
-        <v>57503</v>
+        <v>57506</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2607,7 +2607,7 @@
         <v>123236145</v>
       </c>
       <c r="B20" t="n">
-        <v>90948</v>
+        <v>90953</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>

--- a/artfynd/A 6620-2025 artfynd.xlsx
+++ b/artfynd/A 6620-2025 artfynd.xlsx
@@ -2194,7 +2194,7 @@
         <v>123236897</v>
       </c>
       <c r="B16" t="n">
-        <v>90984</v>
+        <v>90986</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2293,10 +2293,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123236444</v>
+        <v>123236145</v>
       </c>
       <c r="B17" t="n">
-        <v>90988</v>
+        <v>90955</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2305,25 +2305,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2333,10 +2333,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>585270</v>
+        <v>585269</v>
       </c>
       <c r="R17" t="n">
-        <v>7041198</v>
+        <v>7041239</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2398,7 +2398,7 @@
         <v>123236869</v>
       </c>
       <c r="B18" t="n">
-        <v>78786</v>
+        <v>78788</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2500,7 +2500,7 @@
         <v>123231136</v>
       </c>
       <c r="B19" t="n">
-        <v>57506</v>
+        <v>57507</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2604,10 +2604,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123236145</v>
+        <v>123236444</v>
       </c>
       <c r="B20" t="n">
-        <v>90953</v>
+        <v>90990</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2616,25 +2616,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2644,10 +2644,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>585269</v>
+        <v>585270</v>
       </c>
       <c r="R20" t="n">
-        <v>7041239</v>
+        <v>7041198</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>

--- a/artfynd/A 6620-2025 artfynd.xlsx
+++ b/artfynd/A 6620-2025 artfynd.xlsx
@@ -2191,10 +2191,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123236897</v>
+        <v>123236869</v>
       </c>
       <c r="B16" t="n">
-        <v>90986</v>
+        <v>78788</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2207,21 +2207,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2293,10 +2293,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123236145</v>
+        <v>123236897</v>
       </c>
       <c r="B17" t="n">
-        <v>90955</v>
+        <v>90986</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2305,25 +2305,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5447</v>
+        <v>1108</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2333,10 +2333,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>585269</v>
+        <v>585327</v>
       </c>
       <c r="R17" t="n">
-        <v>7041239</v>
+        <v>7041140</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2395,10 +2395,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123236869</v>
+        <v>123231136</v>
       </c>
       <c r="B18" t="n">
-        <v>78788</v>
+        <v>57507</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2411,34 +2411,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Långstranden, Långstranden, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>585327</v>
+        <v>585384</v>
       </c>
       <c r="R18" t="n">
-        <v>7041140</v>
+        <v>7041145</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2497,10 +2502,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123231136</v>
+        <v>123236145</v>
       </c>
       <c r="B19" t="n">
-        <v>57507</v>
+        <v>90955</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2509,43 +2514,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Långstranden, Långstranden, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>585384</v>
+        <v>585269</v>
       </c>
       <c r="R19" t="n">
-        <v>7041145</v>
+        <v>7041239</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
